--- a/artfynd/S 1081-2025 artfynd.xlsx
+++ b/artfynd/S 1081-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY51"/>
+  <dimension ref="A1:AZ51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482561</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134472604</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134472636</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482565</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482566</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482567</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1356,6 +1391,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482540</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1458,6 +1498,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482541</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1560,6 +1605,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482542</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1662,6 +1712,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482543</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1764,6 +1819,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482544</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1866,6 +1926,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482545</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1968,6 +2033,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482546</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2065,6 +2135,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482550</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2162,6 +2237,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482551</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2259,6 +2339,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482552</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2356,6 +2441,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134528037</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2453,6 +2543,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134528038</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2550,6 +2645,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134528039</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2647,6 +2747,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134528040</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2744,6 +2849,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134528041</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2841,6 +2951,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134528042</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2938,6 +3053,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482492</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3035,6 +3155,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482506</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3132,6 +3257,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482507</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3229,6 +3359,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482508</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3326,6 +3461,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134528002</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3423,6 +3563,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482473</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3520,6 +3665,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134472735</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3617,6 +3767,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482484</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3719,6 +3874,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482481</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3821,6 +3981,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482525</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3923,6 +4088,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482526</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4025,6 +4195,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482527</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4127,6 +4302,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482528</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4229,6 +4409,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482529</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4331,6 +4516,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482530</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4433,6 +4623,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482531</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4536,6 +4731,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134528014</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4639,6 +4839,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134528015</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4742,6 +4947,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134528016</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4844,6 +5054,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134528027</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4941,6 +5156,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134528028</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5038,6 +5258,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134528029</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5135,6 +5360,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134473297</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5232,6 +5462,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482486</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5329,6 +5564,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482487</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5426,6 +5666,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134527989</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5523,6 +5768,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482496</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5620,8 +5870,65 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482475</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>